--- a/docs/02_質問回答マトリックス表.xlsx
+++ b/docs/02_質問回答マトリックス表.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B24"/>
+  <dimension ref="B2:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -548,82 +548,110 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>■ 回答スケール（4択）と加点ルール</t>
+          <t>■ 回答スケール（○の大きさで答える7段階の視覚的スケール）と加点ルール</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>各質問には「文言A」「文言B」の2つのステートメントがあり、以下の4段階から回答する。</t>
+          <t>各質問には「文言A」「文言B」の2つのステートメントがあり、以下の7段階（○の大きさで強さを表現）から回答する。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>回答は各質問が属する軸（GH/LT/AV/WC）の a 側・b 側にポイントとして加算される。</t>
+          <t>両端が最も大きい○（強い意思表示）、中央が最も小さい○（どちらとも言えない）という視覚的なデザイン。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　Aに近い　→ a側 +3点 / b側 +0点</t>
+          <t>回答は各質問が属する軸（GH/LT/AV/WC）の a 側・b 側にポイントとして加算される。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　ややA　　→ a側 +2点 / b側 +1点</t>
+          <t xml:space="preserve">　Aに最も近い(●○○○○○○) → a側 +6点 / b側 +0点</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　ややB　　→ a側 +1点 / b側 +2点</t>
+          <t xml:space="preserve">　やや強くA　　　　　　　→ a側 +5点 / b側 +1点</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　Bに近い　→ a側 +0点 / b側 +3点</t>
+          <t xml:space="preserve">　ややA　　　　　　　　　→ a側 +4点 / b側 +2点</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1問あたり配点は必ず合計3点（a+b=3）。6問×3点=軸ごと最大18点。</t>
+          <t xml:space="preserve">　どちらとも言えない　　　→ a側 +3点 / b側 +3点</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ややB　　　　　　　　　→ a側 +2点 / b側 +4点</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>■ 16タイプ判定ロジック</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　やや強くB　　　　　　　→ a側 +1点 / b側 +5点</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>各軸ごとに a側合計・b側合計を百分率に変換し、比率が高い側の文字を採用する（同点はa側優先）。</t>
+          <t xml:space="preserve">　Bに最も近い(○○○○○○●) → a側 +0点 / b側 +6点</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>1問あたり配点は必ず合計6点（a+b=6）。6問×6点=軸ごと最大36点。判定時は百分率に変換するため、配点の絶対値は結果に影響しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>■ 16タイプ判定ロジック</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>各軸ごとに a側合計・b側合計を百分率に変換し、比率が高い側の文字を採用する（同点はa側優先）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>4軸の採用文字（軸1→軸2→軸3→軸4の順）を連結した4文字が最終タイプコード（例：G+L+A+C = GLAC）。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="2" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>セクター診断（Q25〜Q30）は性格タイプの判定には影響せず、独立して「得意になりやすいセクター」を集計する。</t>
         </is>
@@ -640,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -648,12 +676,15 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -694,26 +725,44 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Aに近い
-(a+3/b+0)</t>
+          <t>①Aに最も近い
+(a+6/b+0)</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>ややA
-(a+2/b+1)</t>
+          <t>②
+(a+5/b+1)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>ややB
-(a+1/b+2)</t>
+          <t>③
+(a+4/b+2)</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Bに近い
-(a+0/b+3)</t>
+          <t>④どちらとも言えない
+(a+3/b+3)</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>⑤
+(a+2/b+4)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>⑥
+(a+1/b+5)</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>⑦Bに最も近い
+(a+0/b+6)</t>
         </is>
       </c>
     </row>
@@ -753,22 +802,37 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -808,22 +872,37 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -863,22 +942,37 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -918,22 +1012,37 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -973,22 +1082,37 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1028,22 +1152,37 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1083,22 +1222,37 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1292,37 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1193,22 +1362,37 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1248,22 +1432,37 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1502,37 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1358,22 +1572,37 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1642,37 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1468,22 +1712,37 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1782,37 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1578,22 +1852,37 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1633,22 +1922,37 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1688,22 +1992,37 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1743,22 +2062,37 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1798,22 +2132,37 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1853,22 +2202,37 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1908,22 +2272,37 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1963,22 +2342,37 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -2018,22 +2412,37 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Aに近い(3/0)</t>
+          <t>6/0</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>ややA(2/1)</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>ややB(1/2)</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Bに近い(0/3)</t>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>0/6</t>
         </is>
       </c>
     </row>

--- a/docs/02_質問回答マトリックス表.xlsx
+++ b/docs/02_質問回答マトリックス表.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B28"/>
+  <dimension ref="B2:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -654,6 +654,48 @@
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>セクター診断（Q25〜Q30）は性格タイプの判定には影響せず、独立して「得意になりやすいセクター」を集計する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>■ 4グループ分類（タイプコード先頭2文字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>GL系　🌾 長期・育成・安定系（GLAW / GLAC / GLVW / GLVC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>GT系　🛡️ 慎重・戦略・精密系（GTAW / GTAC / GTVW / GTVC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>HL系　🚀 成長・探索・革新系（HLAW / HLAC / HLVW / HLVC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>HT系　🔥 戦略・トレンド・勝負系（HTAW / HTAC / HTVW / HTVC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>トップページのタイプギャラリーもこの4グループ単位でセクション分けして表示している。</t>
         </is>
       </c>
     </row>
@@ -2885,19 +2927,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2928,27 +2974,47 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>絵文字</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>日本語名</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>英語名</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>相性の良い投資スタイル(上位3)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>代表的投資家（参考例）</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>神話モチーフ</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>キャラクターのセリフ</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>画像</t>
         </is>
       </c>
     </row>
@@ -2980,27 +3046,47 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
+          <t>🌾 長期・育成・安定系</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
           <t>🌳</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>農耕家</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>FARMER</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>高配当株 / 大型株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>ジョン・ボーグル / Vanguard</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>豊穣の女神デメテル</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>「時間は裏切らない。育てたものは必ず実る。」</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3032,27 +3118,47 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>🌾 長期・育成・安定系</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>🏛️</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>資産家</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>WEALTH BUILDER</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>バリュー株 / 大型株 / 個別株</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>ウォーレン・バフェット / Berkshire Hathaway</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>大地の王クロノス</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>「良い土台は、揺れない。価値は静かに積み上がる。」</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3084,27 +3190,47 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>🌾 長期・育成・安定系</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>🌱</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>未来の育成者</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>VISION FARMER</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>成長株 / テーマ株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>森の精霊ドライアド</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>「芽吹く未来を信じる者だけが、森の成長を見届けられる。」</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3136,27 +3262,47 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
+          <t>🌾 長期・育成・安定系</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>🔭</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>先見者</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>VISIONARY</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 成長株 / 中小型株</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>キャシー・ウッド / ARK Invest</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>星読みの賢者オルフェウス</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>「今は小さな光でも、未来では道を照らす星になる。」</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3188,27 +3334,47 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
+          <t>🛡️ 慎重・戦略・精密系</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>🛡️</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>慎重な機動家</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>TACTICAL GUARD</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>高配当株 / バリュー株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>ハワード・マークス / Oaktree Capital</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>北欧の盾戦士ヴァルキュリア</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>「守り抜く者だけが、次の一手を選べる。」</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3240,27 +3406,47 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
+          <t>🛡️ 慎重・戦略・精密系</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>🎯</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>精密投資家</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>PRECISION TRADER</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>バリュー株 / 個別株 / 中小型株</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>マイケル・スタインハルト</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>影の射手エルフレンジャー</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>「狙うのは一つでいい。確信だけが矢を放つ。」</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3292,27 +3478,47 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
+          <t>🛡️ 慎重・戦略・精密系</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>🦊</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>機会探索者</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>OPPORTUNITY SCOUT</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 成長株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>ジョージ・ソロス</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>商人の精霊メルクリウス</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>「風向きは常に変わる。だからこそ、面白い。」</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3344,27 +3550,47 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
+          <t>🛡️ 慎重・戦略・精密系</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>⚡</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>機会狩猟者</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>MARKET HUNTER</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 中小型株 / 個別株</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>ポール・チューダー・ジョーンズ</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>雷の獣人ライカンスロープ</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>「雷は一瞬だ。掴める者だけが力に変える。」</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3396,27 +3622,47 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
+          <t>🚀 成長・探索・革新系</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
           <t>🌾</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>成長農家</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>GROWTH FARMER</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>成長株 / 中小型株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>ピーター・リンチ</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>春の女神ペルセポネ</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>「春は必ず来る。信じて育てた者だけが花を見る。」</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3448,27 +3694,47 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
+          <t>🚀 成長・探索・革新系</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
           <t>🦅</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>成長狩人</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>GROWTH HUNTER</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>成長株 / 中小型株 / テーマ株</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>フィリップ・フィッシャー</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>鷹神ホルス</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>「高く飛ぶほど、未来の形がよく見える。」</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3500,27 +3766,47 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>🚀 成長・探索・革新系</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>🚀</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>未来探索者</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>FUTURE EXPLORER</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 成長株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>星の旅人ヘルメス</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>「まだ見ぬ星を探しに行こう。未来は歩く者に開く。」</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3552,27 +3838,47 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
+          <t>🚀 成長・探索・革新系</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
           <t>🐉</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>開拓者</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>PIONEER</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 成長株 / 個別株</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>ソフトバンクグループ / 孫正義</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>炎竜の契約者ドラグーン</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>「新しい時代は、火を灯す者から始まる。」</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3604,27 +3910,47 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
+          <t>🔥 戦略・トレンド・勝負系</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
           <t>🧠</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>戦略家</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>STRATEGIST</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>成長株 / バリュー株 / ETF・分散投資</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>レイ・ダリオ / Bridgewater</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>戦術の女神アテナ</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>「知恵は最強の盾。戦う前に勝ち筋を読む。」</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3656,27 +3982,47 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
+          <t>🔥 戦略・トレンド・勝負系</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
           <t>🎯</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>スナイパー</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>STOCK SNIPER</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>個別株 / 中小型株 / 成長株</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>チャーリー・マンガー</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>影の狙撃手シャドウエルフ</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>「静かに狙え。雑音のない場所に真実はある。」</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3708,27 +4054,47 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
+          <t>🔥 戦略・トレンド・勝負系</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
           <t>🦊</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>トレンドハンター</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>TREND HUNTER</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 成長株 / 中小型株</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>ジェシー・リバモア</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>情報の狐精霊キツネビ</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>「流れを読むんじゃない。流れの先に立つんだ。」</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3760,27 +4126,47 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
+          <t>🔥 戦略・トレンド・勝負系</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>勝負師</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>SPECULATOR</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>テーマ株 / 中小型株 / 個別株</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>ジム・シモンズ / Renaissance Technologies</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>炎の戦神アレス</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>「火を恐れる者に、勝利の女神は微笑まない。」</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3794,7 +4180,21 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>※代表的投資家はあくまで投資哲学・行動特性が近い参考例であり、本人・機関の公式な診断結果ではない。</t>
+          <t>※グループはタイプコードの先頭2文字（軸1+軸2）で分類（GL/GT/HL/HT の4グループ）。トップページのギャラリーもこの4グループで表示している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>※代表的投資家・神話モチーフ・セリフはあくまで投資スタイルやキャラクター性をイメージするための参考例であり、本人・機関の公式な診断結果ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>※画像列「✓」は images/types/{CODE}.webp にキャラクター画像が実装済みであることを示す（2026年8月17日時点で16タイプ全て実装済み）。</t>
         </is>
       </c>
     </row>
